--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-12</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-13</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25595.55</v>
+        <v>29892.7</v>
       </c>
       <c r="C3" t="n">
-        <v>25595.55</v>
+        <v>29892.7</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17808.14</v>
+        <v>20709.73</v>
       </c>
       <c r="C4" t="n">
-        <v>17808.14</v>
+        <v>20709.73</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29472.34</v>
+        <v>34689.62</v>
       </c>
       <c r="C5" t="n">
-        <v>29472.34</v>
+        <v>34689.62</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17945.93</v>
+        <v>21720.27</v>
       </c>
       <c r="C6" t="n">
-        <v>17945.93</v>
+        <v>21720.27</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6022.98</v>
+        <v>7392.2</v>
       </c>
       <c r="C7" t="n">
-        <v>6022.98</v>
+        <v>7392.2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7954.08</v>
+        <v>9690.559999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>7954.08</v>
+        <v>9690.559999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104799.02</v>
+        <v>124095.08</v>
       </c>
       <c r="C9" t="n">
-        <v>104799.02</v>
+        <v>124095.08</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-13</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-14</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29892.7</v>
+        <v>33588.76</v>
       </c>
       <c r="C3" t="n">
-        <v>29892.7</v>
+        <v>33588.76</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20709.73</v>
+        <v>23354.42</v>
       </c>
       <c r="C4" t="n">
-        <v>20709.73</v>
+        <v>23354.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34689.62</v>
+        <v>38559.19</v>
       </c>
       <c r="C5" t="n">
-        <v>34689.62</v>
+        <v>38559.19</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21720.27</v>
+        <v>25357.1</v>
       </c>
       <c r="C6" t="n">
-        <v>21720.27</v>
+        <v>25357.1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7392.2</v>
+        <v>8485.58</v>
       </c>
       <c r="C7" t="n">
-        <v>7392.2</v>
+        <v>8485.58</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9690.559999999999</v>
+        <v>11376.73</v>
       </c>
       <c r="C8" t="n">
-        <v>9690.559999999999</v>
+        <v>11376.73</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124095.08</v>
+        <v>140721.78</v>
       </c>
       <c r="C9" t="n">
-        <v>124095.08</v>
+        <v>140721.78</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-14</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-15</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33588.76</v>
+        <v>34992.63</v>
       </c>
       <c r="C3" t="n">
-        <v>33588.76</v>
+        <v>34992.63</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23354.42</v>
+        <v>23763.85</v>
       </c>
       <c r="C4" t="n">
-        <v>23354.42</v>
+        <v>23763.85</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38559.19</v>
+        <v>40613.57</v>
       </c>
       <c r="C5" t="n">
-        <v>38559.19</v>
+        <v>40613.57</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25357.1</v>
+        <v>27211.34</v>
       </c>
       <c r="C6" t="n">
-        <v>25357.1</v>
+        <v>27211.34</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8485.58</v>
+        <v>9259.65</v>
       </c>
       <c r="C7" t="n">
-        <v>8485.58</v>
+        <v>9259.65</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11376.73</v>
+        <v>13140.11</v>
       </c>
       <c r="C8" t="n">
-        <v>11376.73</v>
+        <v>13140.11</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140721.78</v>
+        <v>148981.15</v>
       </c>
       <c r="C9" t="n">
-        <v>140721.78</v>
+        <v>148981.15</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-15</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-16</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34992.63</v>
+        <v>36804.65</v>
       </c>
       <c r="C3" t="n">
-        <v>34992.63</v>
+        <v>36804.65</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23763.85</v>
+        <v>24117.45</v>
       </c>
       <c r="C4" t="n">
-        <v>23763.85</v>
+        <v>24117.45</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40613.57</v>
+        <v>42469.21</v>
       </c>
       <c r="C5" t="n">
-        <v>40613.57</v>
+        <v>42469.21</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27211.34</v>
+        <v>27630.05</v>
       </c>
       <c r="C6" t="n">
-        <v>27211.34</v>
+        <v>27630.05</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9259.65</v>
+        <v>10187.89</v>
       </c>
       <c r="C7" t="n">
-        <v>9259.65</v>
+        <v>10187.89</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13140.11</v>
+        <v>13637.55</v>
       </c>
       <c r="C8" t="n">
-        <v>13140.11</v>
+        <v>13637.55</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>148981.15</v>
+        <v>154846.8</v>
       </c>
       <c r="C9" t="n">
-        <v>148981.15</v>
+        <v>154846.8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-16</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-17</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36804.65</v>
+        <v>38344.16</v>
       </c>
       <c r="C3" t="n">
-        <v>36804.65</v>
+        <v>38344.16</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24117.45</v>
+        <v>24758.95</v>
       </c>
       <c r="C4" t="n">
-        <v>24117.45</v>
+        <v>24758.95</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42469.21</v>
+        <v>44950.64</v>
       </c>
       <c r="C5" t="n">
-        <v>42469.21</v>
+        <v>44950.64</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27630.05</v>
+        <v>28367.24</v>
       </c>
       <c r="C6" t="n">
-        <v>27630.05</v>
+        <v>28367.24</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10187.89</v>
+        <v>10997.82</v>
       </c>
       <c r="C7" t="n">
-        <v>10187.89</v>
+        <v>10997.82</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13637.55</v>
+        <v>14083.75</v>
       </c>
       <c r="C8" t="n">
-        <v>13637.55</v>
+        <v>14083.75</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154846.8</v>
+        <v>161502.56</v>
       </c>
       <c r="C9" t="n">
-        <v>154846.8</v>
+        <v>161502.56</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-17</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-18</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38344.16</v>
+        <v>39629.39</v>
       </c>
       <c r="C3" t="n">
-        <v>38344.16</v>
+        <v>39629.39</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24758.95</v>
+        <v>25046.27</v>
       </c>
       <c r="C4" t="n">
-        <v>24758.95</v>
+        <v>25046.27</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44950.64</v>
+        <v>47222.99</v>
       </c>
       <c r="C5" t="n">
-        <v>44950.64</v>
+        <v>47222.99</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28367.24</v>
+        <v>29245.99</v>
       </c>
       <c r="C6" t="n">
-        <v>28367.24</v>
+        <v>29245.99</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10997.82</v>
+        <v>11654.51</v>
       </c>
       <c r="C7" t="n">
-        <v>10997.82</v>
+        <v>11654.51</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14083.75</v>
+        <v>14576.67</v>
       </c>
       <c r="C8" t="n">
-        <v>14083.75</v>
+        <v>14576.67</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161502.56</v>
+        <v>167375.82</v>
       </c>
       <c r="C9" t="n">
-        <v>161502.56</v>
+        <v>167375.82</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-18</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-19</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39629.39</v>
+        <v>42561.26</v>
       </c>
       <c r="C3" t="n">
-        <v>39629.39</v>
+        <v>42561.26</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25046.27</v>
+        <v>25904.1</v>
       </c>
       <c r="C4" t="n">
-        <v>25046.27</v>
+        <v>25904.1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47222.99</v>
+        <v>50027.89</v>
       </c>
       <c r="C5" t="n">
-        <v>47222.99</v>
+        <v>50027.89</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29245.99</v>
+        <v>31488.64</v>
       </c>
       <c r="C6" t="n">
-        <v>29245.99</v>
+        <v>31488.64</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11654.51</v>
+        <v>12682.42</v>
       </c>
       <c r="C7" t="n">
-        <v>11654.51</v>
+        <v>12682.42</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14576.67</v>
+        <v>15847.17</v>
       </c>
       <c r="C8" t="n">
-        <v>14576.67</v>
+        <v>15847.17</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167375.82</v>
+        <v>178511.48</v>
       </c>
       <c r="C9" t="n">
-        <v>167375.82</v>
+        <v>178511.48</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-19</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-20</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42561.26</v>
+        <v>47200.31</v>
       </c>
       <c r="C3" t="n">
-        <v>42561.26</v>
+        <v>47200.31</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25904.1</v>
+        <v>29402.46</v>
       </c>
       <c r="C4" t="n">
-        <v>25904.1</v>
+        <v>29402.46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50027.89</v>
+        <v>54314.88</v>
       </c>
       <c r="C5" t="n">
-        <v>50027.89</v>
+        <v>54314.88</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31488.64</v>
+        <v>34535.71</v>
       </c>
       <c r="C6" t="n">
-        <v>31488.64</v>
+        <v>34535.71</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12682.42</v>
+        <v>14177.25</v>
       </c>
       <c r="C7" t="n">
-        <v>12682.42</v>
+        <v>14177.25</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15847.17</v>
+        <v>17170.66</v>
       </c>
       <c r="C8" t="n">
-        <v>15847.17</v>
+        <v>17170.66</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>178511.48</v>
+        <v>196801.27</v>
       </c>
       <c r="C9" t="n">
-        <v>178511.48</v>
+        <v>196801.27</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-20</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-21</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47200.31</v>
+        <v>51268.44</v>
       </c>
       <c r="C3" t="n">
-        <v>47200.31</v>
+        <v>51268.44</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29402.46</v>
+        <v>31679.74</v>
       </c>
       <c r="C4" t="n">
-        <v>29402.46</v>
+        <v>31679.74</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54314.88</v>
+        <v>58129.21</v>
       </c>
       <c r="C5" t="n">
-        <v>54314.88</v>
+        <v>58129.21</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34535.71</v>
+        <v>36795.56</v>
       </c>
       <c r="C6" t="n">
-        <v>34535.71</v>
+        <v>36795.56</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14177.25</v>
+        <v>15060.07</v>
       </c>
       <c r="C7" t="n">
-        <v>14177.25</v>
+        <v>15060.07</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17170.66</v>
+        <v>18481.13</v>
       </c>
       <c r="C8" t="n">
-        <v>17170.66</v>
+        <v>18481.13</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196801.27</v>
+        <v>211414.15</v>
       </c>
       <c r="C9" t="n">
-        <v>196801.27</v>
+        <v>211414.15</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-21</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-22</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51268.44</v>
+        <v>53232.63</v>
       </c>
       <c r="C3" t="n">
-        <v>51268.44</v>
+        <v>53232.63</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31679.74</v>
+        <v>32194.12</v>
       </c>
       <c r="C4" t="n">
-        <v>31679.74</v>
+        <v>32194.12</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58129.21</v>
+        <v>59992.43</v>
       </c>
       <c r="C5" t="n">
-        <v>58129.21</v>
+        <v>59992.43</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36795.56</v>
+        <v>37522.56</v>
       </c>
       <c r="C6" t="n">
-        <v>36795.56</v>
+        <v>37522.56</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15060.07</v>
+        <v>15562.84</v>
       </c>
       <c r="C7" t="n">
-        <v>15060.07</v>
+        <v>15562.84</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18481.13</v>
+        <v>18969.96</v>
       </c>
       <c r="C8" t="n">
-        <v>18481.13</v>
+        <v>18969.96</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211414.15</v>
+        <v>217474.54</v>
       </c>
       <c r="C9" t="n">
-        <v>211414.15</v>
+        <v>217474.54</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-22</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-23</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53232.63</v>
+        <v>55099.09</v>
       </c>
       <c r="C3" t="n">
-        <v>53232.63</v>
+        <v>55099.09</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32194.12</v>
+        <v>33648.1</v>
       </c>
       <c r="C4" t="n">
-        <v>32194.12</v>
+        <v>33648.1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59992.43</v>
+        <v>62473.33</v>
       </c>
       <c r="C5" t="n">
-        <v>59992.43</v>
+        <v>62473.33</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37522.56</v>
+        <v>38595.68</v>
       </c>
       <c r="C6" t="n">
-        <v>37522.56</v>
+        <v>38595.68</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15562.84</v>
+        <v>16355.07</v>
       </c>
       <c r="C7" t="n">
-        <v>15562.84</v>
+        <v>16355.07</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18969.96</v>
+        <v>19766.16</v>
       </c>
       <c r="C8" t="n">
-        <v>18969.96</v>
+        <v>19766.16</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>217474.54</v>
+        <v>225937.43</v>
       </c>
       <c r="C9" t="n">
-        <v>217474.54</v>
+        <v>225937.43</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-23</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-24</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55099.09</v>
+        <v>56885.22</v>
       </c>
       <c r="C3" t="n">
-        <v>55099.09</v>
+        <v>56885.22</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33648.1</v>
+        <v>34584.6</v>
       </c>
       <c r="C4" t="n">
-        <v>33648.1</v>
+        <v>34584.6</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62473.33</v>
+        <v>64671.91</v>
       </c>
       <c r="C5" t="n">
-        <v>62473.33</v>
+        <v>64671.91</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38595.68</v>
+        <v>39512.9</v>
       </c>
       <c r="C6" t="n">
-        <v>38595.68</v>
+        <v>39512.9</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16355.07</v>
+        <v>16865.77</v>
       </c>
       <c r="C7" t="n">
-        <v>16355.07</v>
+        <v>16865.77</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19766.16</v>
+        <v>20406.24</v>
       </c>
       <c r="C8" t="n">
-        <v>19766.16</v>
+        <v>20406.24</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>225937.43</v>
+        <v>232926.64</v>
       </c>
       <c r="C9" t="n">
-        <v>225937.43</v>
+        <v>232926.64</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-24</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-25</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56885.22</v>
+        <v>58773.27</v>
       </c>
       <c r="C3" t="n">
-        <v>56885.22</v>
+        <v>58773.27</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34584.6</v>
+        <v>35292.07</v>
       </c>
       <c r="C4" t="n">
-        <v>34584.6</v>
+        <v>35292.07</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64671.91</v>
+        <v>66888.24000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>64671.91</v>
+        <v>66888.24000000001</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39512.9</v>
+        <v>40449.26</v>
       </c>
       <c r="C6" t="n">
-        <v>39512.9</v>
+        <v>40449.26</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16865.77</v>
+        <v>17294.18</v>
       </c>
       <c r="C7" t="n">
-        <v>16865.77</v>
+        <v>17294.18</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20406.24</v>
+        <v>21351.89</v>
       </c>
       <c r="C8" t="n">
-        <v>20406.24</v>
+        <v>21351.89</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232926.64</v>
+        <v>240048.91</v>
       </c>
       <c r="C9" t="n">
-        <v>232926.64</v>
+        <v>240048.91</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-25</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-26</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58773.27</v>
+        <v>61452.23</v>
       </c>
       <c r="C3" t="n">
-        <v>58773.27</v>
+        <v>61452.23</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35292.07</v>
+        <v>36144.55</v>
       </c>
       <c r="C4" t="n">
-        <v>35292.07</v>
+        <v>36144.55</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66888.24000000001</v>
+        <v>69242.61</v>
       </c>
       <c r="C5" t="n">
-        <v>66888.24000000001</v>
+        <v>69242.61</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40449.26</v>
+        <v>42628.09</v>
       </c>
       <c r="C6" t="n">
-        <v>40449.26</v>
+        <v>42628.09</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17294.18</v>
+        <v>17637.7</v>
       </c>
       <c r="C7" t="n">
-        <v>17294.18</v>
+        <v>17637.7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21351.89</v>
+        <v>22137.85</v>
       </c>
       <c r="C8" t="n">
-        <v>21351.89</v>
+        <v>22137.85</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240048.91</v>
+        <v>249243.03</v>
       </c>
       <c r="C9" t="n">
-        <v>240048.91</v>
+        <v>249243.03</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-26</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-27</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61452.23</v>
+        <v>65972.50999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>61452.23</v>
+        <v>65972.50999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36144.55</v>
+        <v>39111.17</v>
       </c>
       <c r="C4" t="n">
-        <v>36144.55</v>
+        <v>39111.17</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69242.61</v>
+        <v>73534.38</v>
       </c>
       <c r="C5" t="n">
-        <v>69242.61</v>
+        <v>73534.38</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42628.09</v>
+        <v>46005.36</v>
       </c>
       <c r="C6" t="n">
-        <v>42628.09</v>
+        <v>46005.36</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17637.7</v>
+        <v>18217.55</v>
       </c>
       <c r="C7" t="n">
-        <v>17637.7</v>
+        <v>18217.55</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22137.85</v>
+        <v>23548.23</v>
       </c>
       <c r="C8" t="n">
-        <v>22137.85</v>
+        <v>23548.23</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>249243.03</v>
+        <v>266389.2</v>
       </c>
       <c r="C9" t="n">
-        <v>249243.03</v>
+        <v>266389.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-27</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-28</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65972.50999999999</v>
+        <v>69193.74000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>65972.50999999999</v>
+        <v>69193.74000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39111.17</v>
+        <v>41273.1</v>
       </c>
       <c r="C4" t="n">
-        <v>39111.17</v>
+        <v>41273.1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73534.38</v>
+        <v>77969.31</v>
       </c>
       <c r="C5" t="n">
-        <v>73534.38</v>
+        <v>77969.31</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46005.36</v>
+        <v>48735.4</v>
       </c>
       <c r="C6" t="n">
-        <v>46005.36</v>
+        <v>48735.4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18217.55</v>
+        <v>18621.46</v>
       </c>
       <c r="C7" t="n">
-        <v>18217.55</v>
+        <v>18621.46</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23548.23</v>
+        <v>24952.41</v>
       </c>
       <c r="C8" t="n">
-        <v>23548.23</v>
+        <v>24952.41</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>266389.2</v>
+        <v>280745.42</v>
       </c>
       <c r="C9" t="n">
-        <v>266389.2</v>
+        <v>280745.42</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-28</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-29</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69193.74000000001</v>
+        <v>70562.24000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>69193.74000000001</v>
+        <v>70562.24000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41273.1</v>
+        <v>41841.78</v>
       </c>
       <c r="C4" t="n">
-        <v>41273.1</v>
+        <v>41841.78</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77969.31</v>
+        <v>79930.78</v>
       </c>
       <c r="C5" t="n">
-        <v>77969.31</v>
+        <v>79930.78</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48735.4</v>
+        <v>49421.2</v>
       </c>
       <c r="C6" t="n">
-        <v>48735.4</v>
+        <v>49421.2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18621.46</v>
+        <v>18778.43</v>
       </c>
       <c r="C7" t="n">
-        <v>18621.46</v>
+        <v>18778.43</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24952.41</v>
+        <v>25411.01</v>
       </c>
       <c r="C8" t="n">
-        <v>24952.41</v>
+        <v>25411.01</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>280745.42</v>
+        <v>285945.44</v>
       </c>
       <c r="C9" t="n">
-        <v>280745.42</v>
+        <v>285945.44</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-29</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-30</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70562.24000000001</v>
+        <v>72130.14999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>70562.24000000001</v>
+        <v>72130.14999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41841.78</v>
+        <v>42168.89</v>
       </c>
       <c r="C4" t="n">
-        <v>41841.78</v>
+        <v>42168.89</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79930.78</v>
+        <v>81206.7</v>
       </c>
       <c r="C5" t="n">
-        <v>79930.78</v>
+        <v>81206.7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49421.2</v>
+        <v>51319.38</v>
       </c>
       <c r="C6" t="n">
-        <v>49421.2</v>
+        <v>51319.38</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18778.43</v>
+        <v>19348.98</v>
       </c>
       <c r="C7" t="n">
-        <v>18778.43</v>
+        <v>19348.98</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25411.01</v>
+        <v>27634.87</v>
       </c>
       <c r="C8" t="n">
-        <v>25411.01</v>
+        <v>27634.87</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>285945.44</v>
+        <v>293808.97</v>
       </c>
       <c r="C9" t="n">
-        <v>285945.44</v>
+        <v>293808.97</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-30</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-01</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72130.14999999999</v>
+        <v>1424.39</v>
       </c>
       <c r="C3" t="n">
-        <v>72130.14999999999</v>
+        <v>1424.39</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42168.89</v>
+        <v>1098.18</v>
       </c>
       <c r="C4" t="n">
-        <v>42168.89</v>
+        <v>1098.18</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81206.7</v>
+        <v>1540.68</v>
       </c>
       <c r="C5" t="n">
-        <v>81206.7</v>
+        <v>1540.68</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51319.38</v>
+        <v>1221.15</v>
       </c>
       <c r="C6" t="n">
-        <v>51319.38</v>
+        <v>1221.15</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19348.98</v>
+        <v>742.99</v>
       </c>
       <c r="C7" t="n">
-        <v>19348.98</v>
+        <v>742.99</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27634.87</v>
+        <v>464.95</v>
       </c>
       <c r="C8" t="n">
-        <v>27634.87</v>
+        <v>464.95</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>293808.97</v>
+        <v>6492.339999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>293808.97</v>
+        <v>6492.339999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-01</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-02</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1424.39</v>
+        <v>3295.21</v>
       </c>
       <c r="C3" t="n">
-        <v>1424.39</v>
+        <v>3295.21</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1098.18</v>
+        <v>2572.96</v>
       </c>
       <c r="C4" t="n">
-        <v>1098.18</v>
+        <v>2572.96</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1540.68</v>
+        <v>3886.3</v>
       </c>
       <c r="C5" t="n">
-        <v>1540.68</v>
+        <v>3886.3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1221.15</v>
+        <v>2658.68</v>
       </c>
       <c r="C6" t="n">
-        <v>1221.15</v>
+        <v>2658.68</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>742.99</v>
+        <v>1493.41</v>
       </c>
       <c r="C7" t="n">
-        <v>742.99</v>
+        <v>1493.41</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>464.95</v>
+        <v>1027.4</v>
       </c>
       <c r="C8" t="n">
-        <v>464.95</v>
+        <v>1027.4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6492.339999999999</v>
+        <v>14933.96</v>
       </c>
       <c r="C9" t="n">
-        <v>6492.339999999999</v>
+        <v>14933.96</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-02</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-03</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3295.21</v>
+        <v>5279.87</v>
       </c>
       <c r="C3" t="n">
-        <v>3295.21</v>
+        <v>5279.87</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2572.96</v>
+        <v>3505.42</v>
       </c>
       <c r="C4" t="n">
-        <v>2572.96</v>
+        <v>3505.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3886.3</v>
+        <v>6393.86</v>
       </c>
       <c r="C5" t="n">
-        <v>3886.3</v>
+        <v>6393.86</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2658.68</v>
+        <v>5326.97</v>
       </c>
       <c r="C6" t="n">
-        <v>2658.68</v>
+        <v>5326.97</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1493.41</v>
+        <v>2476.83</v>
       </c>
       <c r="C7" t="n">
-        <v>1493.41</v>
+        <v>2476.83</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1027.4</v>
+        <v>2151.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1027.4</v>
+        <v>2151.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14933.96</v>
+        <v>25134.45</v>
       </c>
       <c r="C9" t="n">
-        <v>14933.96</v>
+        <v>25134.45</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-03</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-04</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5279.87</v>
+        <v>9987.09</v>
       </c>
       <c r="C3" t="n">
-        <v>5279.87</v>
+        <v>9987.09</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3505.42</v>
+        <v>6283.92</v>
       </c>
       <c r="C4" t="n">
-        <v>3505.42</v>
+        <v>6283.92</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6393.86</v>
+        <v>11053.17</v>
       </c>
       <c r="C5" t="n">
-        <v>6393.86</v>
+        <v>11053.17</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5326.97</v>
+        <v>8769.66</v>
       </c>
       <c r="C6" t="n">
-        <v>5326.97</v>
+        <v>8769.66</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2476.83</v>
+        <v>3432.69</v>
       </c>
       <c r="C7" t="n">
-        <v>2476.83</v>
+        <v>3432.69</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2151.5</v>
+        <v>3584.15</v>
       </c>
       <c r="C8" t="n">
-        <v>2151.5</v>
+        <v>3584.15</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25134.45</v>
+        <v>43110.68</v>
       </c>
       <c r="C9" t="n">
-        <v>25134.45</v>
+        <v>43110.68</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-04</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-05</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9987.09</v>
+        <v>13438.42</v>
       </c>
       <c r="C3" t="n">
-        <v>9987.09</v>
+        <v>13438.42</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6283.92</v>
+        <v>8235.07</v>
       </c>
       <c r="C4" t="n">
-        <v>6283.92</v>
+        <v>8235.07</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11053.17</v>
+        <v>15213.78</v>
       </c>
       <c r="C5" t="n">
-        <v>11053.17</v>
+        <v>15213.78</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8769.66</v>
+        <v>11520.81</v>
       </c>
       <c r="C6" t="n">
-        <v>8769.66</v>
+        <v>11520.81</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3432.69</v>
+        <v>4515.67</v>
       </c>
       <c r="C7" t="n">
-        <v>3432.69</v>
+        <v>4515.67</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3584.15</v>
+        <v>5163.33</v>
       </c>
       <c r="C8" t="n">
-        <v>3584.15</v>
+        <v>5163.33</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43110.68</v>
+        <v>58087.07999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>43110.68</v>
+        <v>58087.07999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-05</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-06</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13438.42</v>
+        <v>15369.75</v>
       </c>
       <c r="C3" t="n">
-        <v>13438.42</v>
+        <v>15369.75</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8235.07</v>
+        <v>9150.280000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>8235.07</v>
+        <v>9150.280000000001</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15213.78</v>
+        <v>17005.91</v>
       </c>
       <c r="C5" t="n">
-        <v>15213.78</v>
+        <v>17005.91</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11520.81</v>
+        <v>12209.14</v>
       </c>
       <c r="C6" t="n">
-        <v>11520.81</v>
+        <v>12209.14</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4515.67</v>
+        <v>5387.07</v>
       </c>
       <c r="C7" t="n">
-        <v>4515.67</v>
+        <v>5387.07</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5163.33</v>
+        <v>5624.98</v>
       </c>
       <c r="C8" t="n">
-        <v>5163.33</v>
+        <v>5624.98</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58087.07999999999</v>
+        <v>64747.13</v>
       </c>
       <c r="C9" t="n">
-        <v>58087.07999999999</v>
+        <v>64747.13</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-06</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-07</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15369.75</v>
+        <v>17208.17</v>
       </c>
       <c r="C3" t="n">
-        <v>15369.75</v>
+        <v>17208.17</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9150.280000000001</v>
+        <v>9660.18</v>
       </c>
       <c r="C4" t="n">
-        <v>9150.280000000001</v>
+        <v>9660.18</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17005.91</v>
+        <v>19150.69</v>
       </c>
       <c r="C5" t="n">
-        <v>17005.91</v>
+        <v>19150.69</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12209.14</v>
+        <v>13216.93</v>
       </c>
       <c r="C6" t="n">
-        <v>12209.14</v>
+        <v>13216.93</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5387.07</v>
+        <v>6124.96</v>
       </c>
       <c r="C7" t="n">
-        <v>5387.07</v>
+        <v>6124.96</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5624.98</v>
+        <v>6048.21</v>
       </c>
       <c r="C8" t="n">
-        <v>5624.98</v>
+        <v>6048.21</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64747.13</v>
+        <v>71409.14</v>
       </c>
       <c r="C9" t="n">
-        <v>64747.13</v>
+        <v>71409.14</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-07</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-08</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17208.17</v>
+        <v>19081.98</v>
       </c>
       <c r="C3" t="n">
-        <v>17208.17</v>
+        <v>19081.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9660.18</v>
+        <v>10394.94</v>
       </c>
       <c r="C4" t="n">
-        <v>9660.18</v>
+        <v>10394.94</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19150.69</v>
+        <v>21567.54</v>
       </c>
       <c r="C5" t="n">
-        <v>19150.69</v>
+        <v>21567.54</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13216.93</v>
+        <v>14233.78</v>
       </c>
       <c r="C6" t="n">
-        <v>13216.93</v>
+        <v>14233.78</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6124.96</v>
+        <v>6661.33</v>
       </c>
       <c r="C7" t="n">
-        <v>6124.96</v>
+        <v>6661.33</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6048.21</v>
+        <v>6521.23</v>
       </c>
       <c r="C8" t="n">
-        <v>6048.21</v>
+        <v>6521.23</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71409.14</v>
+        <v>78460.79999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>71409.14</v>
+        <v>78460.79999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="4">
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5">
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="6">
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7">
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>5365</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-08</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-09</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19081.98</v>
+        <v>20910.66</v>
       </c>
       <c r="C3" t="n">
-        <v>19081.98</v>
+        <v>20910.66</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1353</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10394.94</v>
+        <v>11846.33</v>
       </c>
       <c r="C4" t="n">
-        <v>10394.94</v>
+        <v>11846.33</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>665</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21567.54</v>
+        <v>23862.26</v>
       </c>
       <c r="C5" t="n">
-        <v>21567.54</v>
+        <v>23862.26</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1470</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14233.78</v>
+        <v>14957.58</v>
       </c>
       <c r="C6" t="n">
-        <v>14233.78</v>
+        <v>14957.58</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>919</v>
+        <v>969</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6661.33</v>
+        <v>7572.87</v>
       </c>
       <c r="C7" t="n">
-        <v>6661.33</v>
+        <v>7572.87</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>565</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6521.23</v>
+        <v>7091.93</v>
       </c>
       <c r="C8" t="n">
-        <v>6521.23</v>
+        <v>7091.93</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>393</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78460.79999999999</v>
+        <v>86241.63</v>
       </c>
       <c r="C9" t="n">
-        <v>78460.79999999999</v>
+        <v>86241.63</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5365</v>
+        <v>5949</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-09</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-10</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20910.66</v>
+        <v>23468.42</v>
       </c>
       <c r="C3" t="n">
-        <v>20910.66</v>
+        <v>23468.42</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1497</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11846.33</v>
+        <v>13277.54</v>
       </c>
       <c r="C4" t="n">
-        <v>11846.33</v>
+        <v>13277.54</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>762</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23862.26</v>
+        <v>26581.04</v>
       </c>
       <c r="C5" t="n">
-        <v>23862.26</v>
+        <v>26581.04</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1640</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14957.58</v>
+        <v>17249.51</v>
       </c>
       <c r="C6" t="n">
-        <v>14957.58</v>
+        <v>17249.51</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>969</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7572.87</v>
+        <v>8650.43</v>
       </c>
       <c r="C7" t="n">
-        <v>7572.87</v>
+        <v>8650.43</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>641</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7091.93</v>
+        <v>7903.93</v>
       </c>
       <c r="C8" t="n">
-        <v>7091.93</v>
+        <v>7903.93</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>440</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86241.63</v>
+        <v>97130.87</v>
       </c>
       <c r="C9" t="n">
-        <v>86241.63</v>
+        <v>97130.87</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5949</v>
+        <v>6700</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-10</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-11</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23468.42</v>
+        <v>27789.27</v>
       </c>
       <c r="C3" t="n">
-        <v>23468.42</v>
+        <v>27789.27</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1677</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13277.54</v>
+        <v>18019.85</v>
       </c>
       <c r="C4" t="n">
-        <v>13277.54</v>
+        <v>18019.85</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>856</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26581.04</v>
+        <v>31264.52</v>
       </c>
       <c r="C5" t="n">
-        <v>26581.04</v>
+        <v>31264.52</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1836</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17249.51</v>
+        <v>21478.25</v>
       </c>
       <c r="C6" t="n">
-        <v>17249.51</v>
+        <v>21478.25</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1107</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8650.43</v>
+        <v>9605.030000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>8650.43</v>
+        <v>9605.030000000001</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>730</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7903.93</v>
+        <v>9661.139999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>7903.93</v>
+        <v>9661.139999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>494</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97130.87</v>
+        <v>117818.06</v>
       </c>
       <c r="C9" t="n">
-        <v>97130.87</v>
+        <v>117818.06</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6700</v>
+        <v>8030</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-11</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-12</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27789.27</v>
+        <v>31475.39</v>
       </c>
       <c r="C3" t="n">
-        <v>27789.27</v>
+        <v>31475.39</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1970</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18019.85</v>
+        <v>22131.05</v>
       </c>
       <c r="C4" t="n">
-        <v>18019.85</v>
+        <v>22131.05</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1153</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31264.52</v>
+        <v>34786.03</v>
       </c>
       <c r="C5" t="n">
-        <v>31264.52</v>
+        <v>34786.03</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2140</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21478.25</v>
+        <v>24952.63</v>
       </c>
       <c r="C6" t="n">
-        <v>21478.25</v>
+        <v>24952.63</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1365</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9605.030000000001</v>
+        <v>10501.02</v>
       </c>
       <c r="C7" t="n">
-        <v>9605.030000000001</v>
+        <v>10501.02</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>808</v>
+        <v>887</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9661.139999999999</v>
+        <v>11064.15</v>
       </c>
       <c r="C8" t="n">
-        <v>9661.139999999999</v>
+        <v>11064.15</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>594</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117818.06</v>
+        <v>134910.27</v>
       </c>
       <c r="C9" t="n">
-        <v>117818.06</v>
+        <v>134910.27</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8030</v>
+        <v>9107</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-12</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-13</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31475.39</v>
+        <v>34027.03</v>
       </c>
       <c r="C3" t="n">
-        <v>31475.39</v>
+        <v>34027.03</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2205</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22131.05</v>
+        <v>25773.89</v>
       </c>
       <c r="C4" t="n">
-        <v>22131.05</v>
+        <v>25773.89</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1398</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34786.03</v>
+        <v>37217.9</v>
       </c>
       <c r="C5" t="n">
-        <v>34786.03</v>
+        <v>37217.9</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2372</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24952.63</v>
+        <v>26266.29</v>
       </c>
       <c r="C6" t="n">
-        <v>24952.63</v>
+        <v>26266.29</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1564</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10501.02</v>
+        <v>11015.06</v>
       </c>
       <c r="C7" t="n">
-        <v>10501.02</v>
+        <v>11015.06</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>887</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11064.15</v>
+        <v>11604.49</v>
       </c>
       <c r="C8" t="n">
-        <v>11064.15</v>
+        <v>11604.49</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>681</v>
+        <v>711</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134910.27</v>
+        <v>145904.66</v>
       </c>
       <c r="C9" t="n">
-        <v>134910.27</v>
+        <v>145904.66</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>9107</v>
+        <v>9852</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-13</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-14</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34027.03</v>
+        <v>36058.6</v>
       </c>
       <c r="C3" t="n">
-        <v>34027.03</v>
+        <v>36058.6</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2391</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25773.89</v>
+        <v>26664.44</v>
       </c>
       <c r="C4" t="n">
-        <v>25773.89</v>
+        <v>26664.44</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1617</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37217.9</v>
+        <v>38678.48</v>
       </c>
       <c r="C5" t="n">
-        <v>37217.9</v>
+        <v>38678.48</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2548</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26266.29</v>
+        <v>27145.96</v>
       </c>
       <c r="C6" t="n">
-        <v>26266.29</v>
+        <v>27145.96</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1646</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11015.06</v>
+        <v>11331.89</v>
       </c>
       <c r="C7" t="n">
-        <v>11015.06</v>
+        <v>11331.89</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11604.49</v>
+        <v>12033.95</v>
       </c>
       <c r="C8" t="n">
-        <v>11604.49</v>
+        <v>12033.95</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>711</v>
+        <v>742</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145904.66</v>
+        <v>151913.32</v>
       </c>
       <c r="C9" t="n">
-        <v>145904.66</v>
+        <v>151913.32</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>9852</v>
+        <v>10279</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-14</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-15</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36058.6</v>
+        <v>38238.74</v>
       </c>
       <c r="C3" t="n">
-        <v>36058.6</v>
+        <v>38238.74</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2534</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26664.44</v>
+        <v>27282.42</v>
       </c>
       <c r="C4" t="n">
-        <v>26664.44</v>
+        <v>27282.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1673</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38678.48</v>
+        <v>40573.25</v>
       </c>
       <c r="C5" t="n">
-        <v>38678.48</v>
+        <v>40573.25</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2648</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27145.96</v>
+        <v>29647.41</v>
       </c>
       <c r="C6" t="n">
-        <v>27145.96</v>
+        <v>29647.41</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1711</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11331.89</v>
+        <v>11488.21</v>
       </c>
       <c r="C7" t="n">
-        <v>11331.89</v>
+        <v>11488.21</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>971</v>
+        <v>987</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12033.95</v>
+        <v>12556.24</v>
       </c>
       <c r="C8" t="n">
-        <v>12033.95</v>
+        <v>12556.24</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>742</v>
+        <v>774</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151913.32</v>
+        <v>159786.27</v>
       </c>
       <c r="C9" t="n">
-        <v>151913.32</v>
+        <v>159786.27</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>10279</v>
+        <v>10738</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-15</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-16</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38238.74</v>
+        <v>40209.98</v>
       </c>
       <c r="C3" t="n">
-        <v>38238.74</v>
+        <v>40209.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2692</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27282.42</v>
+        <v>27901.52</v>
       </c>
       <c r="C4" t="n">
-        <v>27282.42</v>
+        <v>27901.52</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1709</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40573.25</v>
+        <v>42884.15</v>
       </c>
       <c r="C5" t="n">
-        <v>40573.25</v>
+        <v>42884.15</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2782</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29647.41</v>
+        <v>30863.06</v>
       </c>
       <c r="C6" t="n">
-        <v>29647.41</v>
+        <v>30863.06</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1794</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11488.21</v>
+        <v>11650.98</v>
       </c>
       <c r="C7" t="n">
-        <v>11488.21</v>
+        <v>11650.98</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>987</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12556.24</v>
+        <v>14104.53</v>
       </c>
       <c r="C8" t="n">
-        <v>12556.24</v>
+        <v>14104.53</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>774</v>
+        <v>805</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>159786.27</v>
+        <v>167614.22</v>
       </c>
       <c r="C9" t="n">
-        <v>159786.27</v>
+        <v>167614.22</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>10738</v>
+        <v>11209</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-16</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-17</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40209.98</v>
+        <v>42610.1</v>
       </c>
       <c r="C3" t="n">
-        <v>40209.98</v>
+        <v>42610.1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2826</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27901.52</v>
+        <v>29036.46</v>
       </c>
       <c r="C4" t="n">
-        <v>27901.52</v>
+        <v>29036.46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1760</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42884.15</v>
+        <v>45300.05</v>
       </c>
       <c r="C5" t="n">
-        <v>42884.15</v>
+        <v>45300.05</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2943</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30863.06</v>
+        <v>33448.74</v>
       </c>
       <c r="C6" t="n">
-        <v>30863.06</v>
+        <v>33448.74</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1869</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11650.98</v>
+        <v>11835.88</v>
       </c>
       <c r="C7" t="n">
-        <v>11650.98</v>
+        <v>11835.88</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1006</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14104.53</v>
+        <v>15063.29</v>
       </c>
       <c r="C8" t="n">
-        <v>14104.53</v>
+        <v>15063.29</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>805</v>
+        <v>863</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167614.22</v>
+        <v>177294.52</v>
       </c>
       <c r="C9" t="n">
-        <v>167614.22</v>
+        <v>177294.52</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>11209</v>
+        <v>11886</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-17</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-18</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42610.1</v>
+        <v>47137.39</v>
       </c>
       <c r="C3" t="n">
-        <v>42610.1</v>
+        <v>47137.39</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3000</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29036.46</v>
+        <v>32178.38</v>
       </c>
       <c r="C4" t="n">
-        <v>29036.46</v>
+        <v>32178.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1843</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45300.05</v>
+        <v>49332.97</v>
       </c>
       <c r="C5" t="n">
-        <v>45300.05</v>
+        <v>49332.97</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3118</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33448.74</v>
+        <v>37719.8</v>
       </c>
       <c r="C6" t="n">
-        <v>33448.74</v>
+        <v>37719.8</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2040</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11835.88</v>
+        <v>13152.44</v>
       </c>
       <c r="C7" t="n">
-        <v>11835.88</v>
+        <v>13152.44</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1022</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15063.29</v>
+        <v>16310.77</v>
       </c>
       <c r="C8" t="n">
-        <v>15063.29</v>
+        <v>16310.77</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>863</v>
+        <v>942</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>177294.52</v>
+        <v>195831.75</v>
       </c>
       <c r="C9" t="n">
-        <v>177294.52</v>
+        <v>195831.75</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>11886</v>
+        <v>13083</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-18</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-19</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47137.39</v>
+        <v>50845.25</v>
       </c>
       <c r="C3" t="n">
-        <v>47137.39</v>
+        <v>50845.25</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3284</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32178.38</v>
+        <v>34668.09</v>
       </c>
       <c r="C4" t="n">
-        <v>32178.38</v>
+        <v>34668.09</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2056</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49332.97</v>
+        <v>52887.51</v>
       </c>
       <c r="C5" t="n">
-        <v>49332.97</v>
+        <v>52887.51</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3386</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37719.8</v>
+        <v>40770.31</v>
       </c>
       <c r="C6" t="n">
-        <v>37719.8</v>
+        <v>40770.31</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2297</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13152.44</v>
+        <v>14170.06</v>
       </c>
       <c r="C7" t="n">
-        <v>13152.44</v>
+        <v>14170.06</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1118</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16310.77</v>
+        <v>17685.51</v>
       </c>
       <c r="C8" t="n">
-        <v>16310.77</v>
+        <v>17685.51</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>942</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>195831.75</v>
+        <v>211026.73</v>
       </c>
       <c r="C9" t="n">
-        <v>195831.75</v>
+        <v>211026.73</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>13083</v>
+        <v>14046</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-19</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-20</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50845.25</v>
+        <v>52561.33</v>
       </c>
       <c r="C3" t="n">
-        <v>50845.25</v>
+        <v>52561.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3515</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34668.09</v>
+        <v>35965.11</v>
       </c>
       <c r="C4" t="n">
-        <v>34668.09</v>
+        <v>35965.11</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2200</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52887.51</v>
+        <v>54693.47</v>
       </c>
       <c r="C5" t="n">
-        <v>52887.51</v>
+        <v>54693.47</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3622</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40770.31</v>
+        <v>41763.89</v>
       </c>
       <c r="C6" t="n">
-        <v>40770.31</v>
+        <v>41763.89</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2482</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14170.06</v>
+        <v>15125.3</v>
       </c>
       <c r="C7" t="n">
-        <v>14170.06</v>
+        <v>15125.3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1205</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17685.51</v>
+        <v>18073.7</v>
       </c>
       <c r="C8" t="n">
-        <v>17685.51</v>
+        <v>18073.7</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1022</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211026.73</v>
+        <v>218182.8</v>
       </c>
       <c r="C9" t="n">
-        <v>211026.73</v>
+        <v>218182.8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>14046</v>
+        <v>14566</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-20</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-21</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52561.33</v>
+        <v>54127.26</v>
       </c>
       <c r="C3" t="n">
-        <v>52561.33</v>
+        <v>54127.26</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3643</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35965.11</v>
+        <v>36437.33</v>
       </c>
       <c r="C4" t="n">
-        <v>35965.11</v>
+        <v>36437.33</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2285</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54693.47</v>
+        <v>56555.36</v>
       </c>
       <c r="C5" t="n">
-        <v>54693.47</v>
+        <v>56555.36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3753</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41763.89</v>
+        <v>42623.84</v>
       </c>
       <c r="C6" t="n">
-        <v>41763.89</v>
+        <v>42623.84</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2552</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15125.3</v>
+        <v>15771.9</v>
       </c>
       <c r="C7" t="n">
-        <v>15125.3</v>
+        <v>15771.9</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1281</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18073.7</v>
+        <v>18753.72</v>
       </c>
       <c r="C8" t="n">
-        <v>18073.7</v>
+        <v>18753.72</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1052</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>218182.8</v>
+        <v>224269.41</v>
       </c>
       <c r="C9" t="n">
-        <v>218182.8</v>
+        <v>224269.41</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>14566</v>
+        <v>15015</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-21</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-22</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54127.26</v>
+        <v>55996.4</v>
       </c>
       <c r="C3" t="n">
-        <v>54127.26</v>
+        <v>55996.4</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3758</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36437.33</v>
+        <v>36826.85</v>
       </c>
       <c r="C4" t="n">
-        <v>36437.33</v>
+        <v>36826.85</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2314</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56555.36</v>
+        <v>58027.54</v>
       </c>
       <c r="C5" t="n">
-        <v>56555.36</v>
+        <v>58027.54</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3889</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42623.84</v>
+        <v>43832.87</v>
       </c>
       <c r="C6" t="n">
-        <v>42623.84</v>
+        <v>43832.87</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2617</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15771.9</v>
+        <v>16506.13</v>
       </c>
       <c r="C7" t="n">
-        <v>15771.9</v>
+        <v>16506.13</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1340</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18753.72</v>
+        <v>19205.62</v>
       </c>
       <c r="C8" t="n">
-        <v>18753.72</v>
+        <v>19205.62</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1097</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>224269.41</v>
+        <v>230395.41</v>
       </c>
       <c r="C9" t="n">
-        <v>224269.41</v>
+        <v>230395.41</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>15015</v>
+        <v>15476</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-22</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-23</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55996.4</v>
+        <v>57759.46</v>
       </c>
       <c r="C3" t="n">
-        <v>55996.4</v>
+        <v>57759.46</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3900</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36826.85</v>
+        <v>37305.41</v>
       </c>
       <c r="C4" t="n">
-        <v>36826.85</v>
+        <v>37305.41</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2341</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58027.54</v>
+        <v>59379.75</v>
       </c>
       <c r="C5" t="n">
-        <v>58027.54</v>
+        <v>59379.75</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4002</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43832.87</v>
+        <v>45094.91</v>
       </c>
       <c r="C6" t="n">
-        <v>43832.87</v>
+        <v>45094.91</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2692</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16506.13</v>
+        <v>17203.39</v>
       </c>
       <c r="C7" t="n">
-        <v>16506.13</v>
+        <v>17203.39</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1414</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19205.62</v>
+        <v>20206.75</v>
       </c>
       <c r="C8" t="n">
-        <v>19205.62</v>
+        <v>20206.75</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1127</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>230395.41</v>
+        <v>236949.67</v>
       </c>
       <c r="C9" t="n">
-        <v>230395.41</v>
+        <v>236949.67</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>15476</v>
+        <v>15955</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-23</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-24</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57759.46</v>
+        <v>59866.82</v>
       </c>
       <c r="C3" t="n">
-        <v>57759.46</v>
+        <v>59866.82</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4038</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37305.41</v>
+        <v>38330.99</v>
       </c>
       <c r="C4" t="n">
-        <v>37305.41</v>
+        <v>38330.99</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2373</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59379.75</v>
+        <v>61337.61</v>
       </c>
       <c r="C5" t="n">
-        <v>59379.75</v>
+        <v>61337.61</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4108</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45094.91</v>
+        <v>47303.71</v>
       </c>
       <c r="C6" t="n">
-        <v>45094.91</v>
+        <v>47303.71</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2776</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17203.39</v>
+        <v>17918.04</v>
       </c>
       <c r="C7" t="n">
-        <v>17203.39</v>
+        <v>17918.04</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1473</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20206.75</v>
+        <v>21249.19</v>
       </c>
       <c r="C8" t="n">
-        <v>20206.75</v>
+        <v>21249.19</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1187</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>236949.67</v>
+        <v>246006.36</v>
       </c>
       <c r="C9" t="n">
-        <v>236949.67</v>
+        <v>246006.36</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>15955</v>
+        <v>16618</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-24</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-25</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59866.82</v>
+        <v>62525.42</v>
       </c>
       <c r="C3" t="n">
-        <v>59866.82</v>
+        <v>62525.42</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4189</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38330.99</v>
+        <v>41669.38</v>
       </c>
       <c r="C4" t="n">
-        <v>38330.99</v>
+        <v>41669.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2440</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61337.61</v>
+        <v>65499.74</v>
       </c>
       <c r="C5" t="n">
-        <v>61337.61</v>
+        <v>65499.74</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4263</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47303.71</v>
+        <v>50700.46</v>
       </c>
       <c r="C6" t="n">
-        <v>47303.71</v>
+        <v>50700.46</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2933</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17918.04</v>
+        <v>19062.88</v>
       </c>
       <c r="C7" t="n">
-        <v>17918.04</v>
+        <v>19062.88</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1541</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21249.19</v>
+        <v>23143.51</v>
       </c>
       <c r="C8" t="n">
-        <v>21249.19</v>
+        <v>23143.51</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1252</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>246006.36</v>
+        <v>262601.39</v>
       </c>
       <c r="C9" t="n">
-        <v>246006.36</v>
+        <v>262601.39</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>16618</v>
+        <v>17681</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-25</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-26</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62525.42</v>
+        <v>65934.09</v>
       </c>
       <c r="C3" t="n">
-        <v>62525.42</v>
+        <v>65934.09</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4376</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41669.38</v>
+        <v>44174.58</v>
       </c>
       <c r="C4" t="n">
-        <v>41669.38</v>
+        <v>44174.58</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2634</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65499.74</v>
+        <v>69323.95</v>
       </c>
       <c r="C5" t="n">
-        <v>65499.74</v>
+        <v>69323.95</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4527</v>
+        <v>4766</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50700.46</v>
+        <v>53347.39</v>
       </c>
       <c r="C6" t="n">
-        <v>50700.46</v>
+        <v>53347.39</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3140</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19062.88</v>
+        <v>19847.62</v>
       </c>
       <c r="C7" t="n">
-        <v>19062.88</v>
+        <v>19847.62</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1637</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23143.51</v>
+        <v>24486.34</v>
       </c>
       <c r="C8" t="n">
-        <v>23143.51</v>
+        <v>24486.34</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1367</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>262601.39</v>
+        <v>277113.97</v>
       </c>
       <c r="C9" t="n">
-        <v>262601.39</v>
+        <v>277113.97</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>17681</v>
+        <v>18603</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-26</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-27</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65934.09</v>
+        <v>67810.42999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>65934.09</v>
+        <v>67810.42999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4598</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44174.58</v>
+        <v>44662.5</v>
       </c>
       <c r="C4" t="n">
-        <v>44174.58</v>
+        <v>44662.5</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2791</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69323.95</v>
+        <v>71093.55</v>
       </c>
       <c r="C5" t="n">
-        <v>69323.95</v>
+        <v>71093.55</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4766</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53347.39</v>
+        <v>54151.98</v>
       </c>
       <c r="C6" t="n">
-        <v>53347.39</v>
+        <v>54151.98</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3296</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19847.62</v>
+        <v>20591.46</v>
       </c>
       <c r="C7" t="n">
-        <v>19847.62</v>
+        <v>20591.46</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1706</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24486.34</v>
+        <v>25049.86</v>
       </c>
       <c r="C8" t="n">
-        <v>24486.34</v>
+        <v>25049.86</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1446</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>277113.97</v>
+        <v>283359.78</v>
       </c>
       <c r="C9" t="n">
-        <v>277113.97</v>
+        <v>283359.78</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>18603</v>
+        <v>19072</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-27</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-28</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67810.42999999999</v>
+        <v>69315.14</v>
       </c>
       <c r="C3" t="n">
-        <v>67810.42999999999</v>
+        <v>69315.14</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4742</v>
+        <v>4858</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44662.5</v>
+        <v>45166.23</v>
       </c>
       <c r="C4" t="n">
-        <v>44662.5</v>
+        <v>45166.23</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2821</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71093.55</v>
+        <v>72775.7</v>
       </c>
       <c r="C5" t="n">
-        <v>71093.55</v>
+        <v>72775.7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4896</v>
+        <v>5025</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54151.98</v>
+        <v>54932.03</v>
       </c>
       <c r="C6" t="n">
-        <v>54151.98</v>
+        <v>54932.03</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3356</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20591.46</v>
+        <v>21055.62</v>
       </c>
       <c r="C7" t="n">
-        <v>20591.46</v>
+        <v>21055.62</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1778</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25049.86</v>
+        <v>25583.71</v>
       </c>
       <c r="C8" t="n">
-        <v>25049.86</v>
+        <v>25583.71</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1479</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>283359.78</v>
+        <v>288828.4300000001</v>
       </c>
       <c r="C9" t="n">
-        <v>283359.78</v>
+        <v>288828.4300000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>19072</v>
+        <v>19476</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-28</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-29</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69315.14</v>
+        <v>71053.46000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>69315.14</v>
+        <v>71053.46000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4858</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45166.23</v>
+        <v>45671.93</v>
       </c>
       <c r="C4" t="n">
-        <v>45166.23</v>
+        <v>45671.93</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2853</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72775.7</v>
+        <v>74988.60000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>72775.7</v>
+        <v>74988.60000000001</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5025</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54932.03</v>
+        <v>56017.33</v>
       </c>
       <c r="C6" t="n">
-        <v>54932.03</v>
+        <v>56017.33</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3410</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21055.62</v>
+        <v>21528.41</v>
       </c>
       <c r="C7" t="n">
-        <v>21055.62</v>
+        <v>21528.41</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1818</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25583.71</v>
+        <v>25995.95</v>
       </c>
       <c r="C8" t="n">
-        <v>25583.71</v>
+        <v>25995.95</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1512</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>288828.4300000001</v>
+        <v>295255.68</v>
       </c>
       <c r="C9" t="n">
-        <v>288828.4300000001</v>
+        <v>295255.68</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>19476</v>
+        <v>19948</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-29</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-30</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71053.46000000001</v>
+        <v>72721.25</v>
       </c>
       <c r="C3" t="n">
-        <v>71053.46000000001</v>
+        <v>72721.25</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4988</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45671.93</v>
+        <v>46744.11</v>
       </c>
       <c r="C4" t="n">
-        <v>45671.93</v>
+        <v>46744.11</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2891</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74988.60000000001</v>
+        <v>76386.89</v>
       </c>
       <c r="C5" t="n">
-        <v>74988.60000000001</v>
+        <v>76386.89</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5184</v>
+        <v>5292</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56017.33</v>
+        <v>57634.18</v>
       </c>
       <c r="C6" t="n">
-        <v>56017.33</v>
+        <v>57634.18</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3485</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21528.41</v>
+        <v>21759.03</v>
       </c>
       <c r="C7" t="n">
-        <v>21528.41</v>
+        <v>21759.03</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1857</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25995.95</v>
+        <v>26752.05</v>
       </c>
       <c r="C8" t="n">
-        <v>25995.95</v>
+        <v>26752.05</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1543</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>295255.68</v>
+        <v>301997.51</v>
       </c>
       <c r="C9" t="n">
-        <v>295255.68</v>
+        <v>301997.51</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>19948</v>
+        <v>20434</v>
       </c>
     </row>
   </sheetData>
